--- a/app1/Excelfiles/March2024_10000.xlsx
+++ b/app1/Excelfiles/March2024_10000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,13 +449,23 @@
     <row r="5"/>
     <row r="6"/>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
